--- a/投资学工作空间/outputs/生产库存销售滞后复算.xlsx
+++ b/投资学工作空间/outputs/生产库存销售滞后复算.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库存与滞后" sheetId="1" r:id="R0fede0ca5ed148d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配对" sheetId="2" r:id="R205f397864ca4bff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原数" sheetId="3" r:id="Raff90b8aa9c14a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库存与滞后" sheetId="1" r:id="Ra53681a3d46f4587"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配对" sheetId="2" r:id="Rff1e45fea7a44335"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原数" sheetId="3" r:id="R6ba9f8a1111247c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -60,8 +60,8 @@
         <x:r>
           <x:t>PDF：sources/annual_reports/pdf/600519_2020_贵州茅台_贵州茅台2020年年度报告_2021-03-30.pdf
 SHA256：464e4c179a18ebea566c5ddc5a4dbcfb83824227e9a10eb1ba0baa23c9d58d2c
-定位：库存12页；产品[13]页
-核验入口：L03-A2020-B</x:t>
+定位：库存12页；产品[13]页；独立总量PDF／报告9页；产销量情况分析表，酒类行库存量列
+核验入口：L03-A2020-B；R2020-08</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -70,8 +70,8 @@
         <x:r>
           <x:t>PDF：sources/annual_reports/pdf/600519_2021_贵州茅台_贵州茅台2021年年度报告_2022-03-30.pdf
 SHA256：f65effdde58bcea99fd6bdb53f61b31d5c432e6dfb2661e5caf05156a433ea5a
-定位：库存13页；产品[14]页
-核验入口：L03-A2021-B</x:t>
+定位：库存13页；产品[14]页；独立总量PDF／报告9页；产销量情况分析表，酒类行库存量列
+核验入口：L03-A2021-B；R2021-08</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -80,8 +80,8 @@
         <x:r>
           <x:t>PDF：sources/annual_reports/pdf/600519_2022_贵州茅台_贵州茅台2022年年度报告_2023-03-30.pdf
 SHA256：de394171306b9f2c7d79f54990de2a9e9c99feb54413150180179e24f0d83358
-定位：库存14页；产品[14, 15]页
-核验入口：L03-A2022-B</x:t>
+定位：库存14页；产品[14, 15]页；独立总量PDF／报告9页；产销量情况分析表，酒类行库存量列
+核验入口：L03-A2022-B；R2022-08</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -90,8 +90,8 @@
         <x:r>
           <x:t>PDF：sources/annual_reports/pdf/600519_2023_贵州茅台_贵州茅台2023年年度报告_2024-04-03.pdf
 SHA256：2125ff97a452ea79b0d784e2432f7d224b6aecc330b644b593477d69e22f4ed1
-定位：库存15页；产品[15]页
-核验入口：L03-A2023-B</x:t>
+定位：库存15页；产品[15]页；独立总量PDF／报告10页；产销量情况分析表，酒类行库存量列
+核验入口：L03-A2023-B；R2023-08</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -100,8 +100,8 @@
         <x:r>
           <x:t>PDF：sources/annual_reports/pdf/600519_2024_贵州茅台_贵州茅台2024年年度报告_2025-04-03.pdf
 SHA256：5299f4940e2ce4e91084b73dc457d558b9d335fa76fbfee6227e4254eb7f4a30
-定位：库存14页；产品[15]页
-核验入口：L03-A2024-B</x:t>
+定位：库存14页；产品[15]页；独立总量PDF／报告9—10页；产销量情况分析表，酒类行库存量列
+核验入口：L03-A2024-B；R2024-24</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -687,13 +687,13 @@
         <x:f>D10/E10</x:f>
         <x:v>0.9666415525363319</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="str">
+      <x:c r="G10" s="11" t="n">
         <x:f>IF(ISNUMBER('原数'!I10),'原数'!I10,"待核")</x:f>
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="str">
+        <x:v>249235.52</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="n">
         <x:f>IF(ISNUMBER(G10),ROUND(G10-E10,2),"待核")</x:f>
-        <x:v>待核</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="1"/>
       <x:c r="J10" s="1"/>
@@ -723,13 +723,13 @@
         <x:f>D11/E11</x:f>
         <x:v>0.9605656719713275</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="str">
+      <x:c r="G11" s="11" t="n">
         <x:f>IF(ISNUMBER('原数'!I11),'原数'!I11,"待核")</x:f>
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="str">
+        <x:v>260746.17</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="n">
         <x:f>IF(ISNUMBER(G11),ROUND(G11-E11,2),"待核")</x:f>
-        <x:v>待核</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="1"/>
       <x:c r="J11" s="1"/>
@@ -759,13 +759,13 @@
         <x:f>D12/E12</x:f>
         <x:v>0.9548292357433399</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="str">
+      <x:c r="G12" s="11" t="n">
         <x:f>IF(ISNUMBER('原数'!I12),'原数'!I12,"待核")</x:f>
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="str">
+        <x:v>276623.17</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="n">
         <x:f>IF(ISNUMBER(G12),ROUND(G12-E12,2),"待核")</x:f>
-        <x:v>待核</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="1"/>
       <x:c r="J12" s="1"/>
@@ -795,13 +795,13 @@
         <x:f>D13/E13</x:f>
         <x:v>0.9523977379354909</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="str">
+      <x:c r="G13" s="11" t="n">
         <x:f>IF(ISNUMBER('原数'!I13),'原数'!I13,"待核")</x:f>
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="str">
+        <x:v>293790.03</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="n">
         <x:f>IF(ISNUMBER(G13),ROUND(G13-E13,2),"待核")</x:f>
-        <x:v>待核</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="1"/>
       <x:c r="J13" s="1"/>
@@ -831,13 +831,13 @@
         <x:f>D14/E14</x:f>
         <x:v>0.9427111595370984</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="str">
+      <x:c r="G14" s="11" t="n">
         <x:f>IF(ISNUMBER('原数'!I14),'原数'!I14,"待核")</x:f>
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="str">
+        <x:v>310008.02</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="n">
         <x:f>IF(ISNUMBER(G14),ROUND(G14-E14,2),"待核")</x:f>
-        <x:v>待核</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="1"/>
       <x:c r="J14" s="1"/>
@@ -5301,12 +5301,14 @@
       <x:c r="H10" s="8" t="n">
         <x:v>240921.41</x:v>
       </x:c>
-      <x:c r="I10" s="8"/>
+      <x:c r="I10" s="8" t="n">
+        <x:v>249235.52</x:v>
+      </x:c>
       <x:c r="J10" s="8" t="n">
         <x:v>84830936002.19</x:v>
       </x:c>
       <x:c r="K10" s="1" t="str">
-        <x:v>L03-A2020-B</x:v>
+        <x:v>L03-A2020-B；R2020-08</x:v>
       </x:c>
       <x:c r="L10" s="1"/>
       <x:c r="M10" s="1"/>
@@ -5334,12 +5336,14 @@
       <x:c r="H11" s="8" t="n">
         <x:v>250463.82</x:v>
       </x:c>
-      <x:c r="I11" s="8"/>
+      <x:c r="I11" s="8" t="n">
+        <x:v>260746.17</x:v>
+      </x:c>
       <x:c r="J11" s="8" t="n">
         <x:v>93464512115.94</x:v>
       </x:c>
       <x:c r="K11" s="1" t="str">
-        <x:v>L03-A2021-B</x:v>
+        <x:v>L03-A2021-B；R2021-08</x:v>
       </x:c>
       <x:c r="L11" s="1"/>
       <x:c r="M11" s="1"/>
@@ -5367,12 +5371,14 @@
       <x:c r="H12" s="8" t="n">
         <x:v>264127.89</x:v>
       </x:c>
-      <x:c r="I12" s="8"/>
+      <x:c r="I12" s="8" t="n">
+        <x:v>276623.17</x:v>
+      </x:c>
       <x:c r="J12" s="8" t="n">
         <x:v>107833685277.94</x:v>
       </x:c>
       <x:c r="K12" s="1" t="str">
-        <x:v>L03-A2022-B</x:v>
+        <x:v>L03-A2022-B；R2022-08</x:v>
       </x:c>
       <x:c r="L12" s="1"/>
       <x:c r="M12" s="1"/>
@@ -5400,12 +5406,14 @@
       <x:c r="H13" s="8" t="n">
         <x:v>279804.96</x:v>
       </x:c>
-      <x:c r="I13" s="8"/>
+      <x:c r="I13" s="8" t="n">
+        <x:v>293790.03</x:v>
+      </x:c>
       <x:c r="J13" s="8" t="n">
         <x:v>126589066691.89</x:v>
       </x:c>
       <x:c r="K13" s="1" t="str">
-        <x:v>L03-A2023-B</x:v>
+        <x:v>L03-A2023-B；R2023-08</x:v>
       </x:c>
       <x:c r="L13" s="1"/>
       <x:c r="M13" s="1"/>
@@ -5433,12 +5441,14 @@
       <x:c r="H14" s="8" t="n">
         <x:v>292248.02</x:v>
       </x:c>
-      <x:c r="I14" s="8"/>
+      <x:c r="I14" s="8" t="n">
+        <x:v>310008.02</x:v>
+      </x:c>
       <x:c r="J14" s="8" t="n">
         <x:v>145928075955.31</x:v>
       </x:c>
       <x:c r="K14" s="1" t="str">
-        <x:v>L03-A2024-B</x:v>
+        <x:v>L03-A2024-B；R2024-24</x:v>
       </x:c>
       <x:c r="L14" s="1"/>
       <x:c r="M14" s="1"/>
@@ -5664,10 +5674,10 @@
         <x:v>贵州茅台2020年年度报告</x:v>
       </x:c>
       <x:c r="D25" s="1" t="str">
-        <x:v>库存12，产销13</x:v>
+        <x:v>库存12，产销13，总量9</x:v>
       </x:c>
       <x:c r="E25" s="1" t="str">
-        <x:v>L03-A2020-B</x:v>
+        <x:v>L03-A2020-B；R2020-08</x:v>
       </x:c>
       <x:c r="F25" s="1"/>
       <x:c r="G25" s="1"/>
@@ -5687,10 +5697,10 @@
         <x:v>贵州茅台2021年年度报告</x:v>
       </x:c>
       <x:c r="D26" s="1" t="str">
-        <x:v>库存13，产销14</x:v>
+        <x:v>库存13，产销14，总量9</x:v>
       </x:c>
       <x:c r="E26" s="1" t="str">
-        <x:v>L03-A2021-B</x:v>
+        <x:v>L03-A2021-B；R2021-08</x:v>
       </x:c>
       <x:c r="F26" s="1"/>
       <x:c r="G26" s="1"/>
@@ -5710,10 +5720,10 @@
         <x:v>贵州茅台2022年年度报告</x:v>
       </x:c>
       <x:c r="D27" s="1" t="str">
-        <x:v>库存14，产销14-15</x:v>
+        <x:v>库存14，产销14-15，总量9</x:v>
       </x:c>
       <x:c r="E27" s="1" t="str">
-        <x:v>L03-A2022-B</x:v>
+        <x:v>L03-A2022-B；R2022-08</x:v>
       </x:c>
       <x:c r="F27" s="1"/>
       <x:c r="G27" s="1"/>
@@ -5733,10 +5743,10 @@
         <x:v>贵州茅台2023年年度报告</x:v>
       </x:c>
       <x:c r="D28" s="1" t="str">
-        <x:v>库存15，产销15</x:v>
+        <x:v>库存15，产销15，总量10</x:v>
       </x:c>
       <x:c r="E28" s="1" t="str">
-        <x:v>L03-A2023-B</x:v>
+        <x:v>L03-A2023-B；R2023-08</x:v>
       </x:c>
       <x:c r="F28" s="1"/>
       <x:c r="G28" s="1"/>
@@ -5756,10 +5766,10 @@
         <x:v>贵州茅台2024年年度报告</x:v>
       </x:c>
       <x:c r="D29" s="1" t="str">
-        <x:v>库存14，产销15</x:v>
+        <x:v>库存14，产销15，总量9-10</x:v>
       </x:c>
       <x:c r="E29" s="1" t="str">
-        <x:v>L03-A2024-B</x:v>
+        <x:v>L03-A2024-B；R2024-24</x:v>
       </x:c>
       <x:c r="F29" s="1"/>
       <x:c r="G29" s="1"/>
@@ -5843,7 +5853,7 @@
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
       <x:c r="B34" s="1" t="str">
-        <x:v>2020—2024独立总库存尚待B04核验，保留空白；成品与半成品已核，不重复确认。</x:v>
+        <x:v>B04已核独立总量；十年库存勾稽均为0吨。原数确认与公式复算分别记录。</x:v>
       </x:c>
       <x:c r="C34" s="1"/>
       <x:c r="D34" s="1"/>
@@ -6087,6 +6097,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42f9747a7b3c4299"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R639510564f384c14"/>
 </x:worksheet>
 </file>